--- a/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MAR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF53729B-0D10-4B60-864E-BC1A32CF2C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FECF145-8BB6-40CD-B68E-D1380BCB8304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -789,13 +789,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH04,S04aH03,S02aH02,S06aH06,S03aH02,S05aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH03,S05aH02,S05aH03,S05aH06,S01aH04,S01aH07,S02aH07,S04aH05,S04aH08,S03aH03,S04aH06,S05aH04,S06aH02,S06aH03,S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S01aH06,S02aH03,S05aH07</t>
+    <t>S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S01aH03,S05aH02,S05aH03,S05aH06,S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S03aH03,S03aH02,S04aH05,S04aH08,S05aH08,S01aH04,S01aH07,S02aH07,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03,S03aH04,S02aH02,S06aH06,S04aH02,S01aH06,S02aH03,S05aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S03aH01,S04aH02,S04aH08,S06aH01,S03aH09,S05aH09,S01aH10,S03aH02,S01aH02,S05aH10,S01aH09,S05aH08,S02aH02,S04aH10,S06aH10,S06aH09,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S01aH01,S04aH01,S06aH02</t>
+    <t>S01aH02,S05aH10,S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S02aH02,S04aH10,S06aH10,S04aH02,S05aH08,S04aH08,S06aH01,S01aH09,S02aH01,S02aH10,S05aH02,S06aH09,S02aH09,S04aH09,S05aH01,S03aH01,S01aH10,S03aH02,S01aH01,S04aH01,S06aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S03aH01,S04aH02,S04aH08,S06aH01,S03aH09,S05aH09,S01aH10,S03aH02,S01aH02,S05aH10,S01aH09,S05aH08,S02aH02,S04aH10,S06aH10,S06aH09,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S01aH01,S04aH01,S06aH02</v>
+        <v>S01aH02,S05aH10,S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S02aH02,S04aH10,S06aH10,S04aH02,S05aH08,S04aH08,S06aH01,S01aH09,S02aH01,S02aH10,S05aH02,S06aH09,S02aH09,S04aH09,S05aH01,S03aH01,S01aH10,S03aH02,S01aH01,S04aH01,S06aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH04,S04aH03,S02aH02,S06aH06,S03aH02,S05aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH03,S05aH02,S05aH03,S05aH06,S01aH04,S01aH07,S02aH07,S04aH05,S04aH08,S03aH03,S04aH06,S05aH04,S06aH02,S06aH03,S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S01aH06,S02aH03,S05aH07</v>
+        <v>S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S01aH03,S05aH02,S05aH03,S05aH06,S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S03aH03,S03aH02,S04aH05,S04aH08,S05aH08,S01aH04,S01aH07,S02aH07,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03,S03aH04,S02aH02,S06aH06,S04aH02,S01aH06,S02aH03,S05aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1518,7 +1518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAA2E85-861D-4FAA-B1CF-706E866CE1E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F44787E-6C7C-4E30-A33A-6FD97838CF66}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1662,7 +1662,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7D4560C-9217-47F1-93A5-86101E3D3FD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39BDC6-3450-469D-8886-5950D3C64FB6}">
   <dimension ref="B9:O1450"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45644,7 +45644,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB10BDF0-9F8D-452D-BF42-28CA4DFE316F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC05B74-719D-4682-AAC9-33D7772551F8}">
   <dimension ref="B9:IV67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -69378,7 +69378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2471AEF4-DB36-49AC-8BC7-6C52F47A3F51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038D0052-FBF6-4FF8-B9B2-472D658BF00D}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -70248,7 +70248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B8C404-46BE-486C-9A41-F94CC69C7F7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC889D7-2D7C-4782-90BD-686339F9CF17}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71595,7 +71595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A798AB2-FED0-4211-9093-F07FA02F2354}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622F57E4-83C8-4E2D-A15C-0058615F6B38}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -72282,7 +72282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F570719A-79D6-4F18-96BF-33430594DEA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76962D5A-38EA-4952-99D7-4BF7FFEE8DF1}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
